--- a/results/04_final_refined_daily_hydroclimate_data/508/Dry_bulb_temp_06h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/508/Dry_bulb_temp_06h00_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="5">
   <si>
     <t>Year</t>
   </si>
@@ -413,8 +413,8 @@
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2">
-        <v>18.4</v>
+      <c r="D2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -427,8 +427,8 @@
       <c r="C3">
         <v>2</v>
       </c>
-      <c r="D3">
-        <v>17.6</v>
+      <c r="D3" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -441,8 +441,8 @@
       <c r="C4">
         <v>3</v>
       </c>
-      <c r="D4">
-        <v>17.4</v>
+      <c r="D4" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -455,8 +455,8 @@
       <c r="C5">
         <v>4</v>
       </c>
-      <c r="D5">
-        <v>20.3</v>
+      <c r="D5" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -469,8 +469,8 @@
       <c r="C6">
         <v>5</v>
       </c>
-      <c r="D6">
-        <v>18.9</v>
+      <c r="D6" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -553,8 +553,8 @@
       <c r="C12">
         <v>11</v>
       </c>
-      <c r="D12">
-        <v>19.2</v>
+      <c r="D12" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -567,8 +567,8 @@
       <c r="C13">
         <v>12</v>
       </c>
-      <c r="D13">
-        <v>18.3</v>
+      <c r="D13" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -581,8 +581,8 @@
       <c r="C14">
         <v>13</v>
       </c>
-      <c r="D14">
-        <v>19.2</v>
+      <c r="D14" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -595,8 +595,8 @@
       <c r="C15">
         <v>14</v>
       </c>
-      <c r="D15">
-        <v>19.4</v>
+      <c r="D15" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -609,8 +609,8 @@
       <c r="C16">
         <v>15</v>
       </c>
-      <c r="D16">
-        <v>18</v>
+      <c r="D16" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:4">

--- a/results/04_final_refined_daily_hydroclimate_data/508/Dry_bulb_temp_06h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/508/Dry_bulb_temp_06h00_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="5">
   <si>
     <t>Year</t>
   </si>
@@ -413,8 +413,8 @@
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2" t="s">
-        <v>4</v>
+      <c r="D2">
+        <v>18.4</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -427,8 +427,8 @@
       <c r="C3">
         <v>2</v>
       </c>
-      <c r="D3" t="s">
-        <v>4</v>
+      <c r="D3">
+        <v>17.6</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -441,8 +441,8 @@
       <c r="C4">
         <v>3</v>
       </c>
-      <c r="D4" t="s">
-        <v>4</v>
+      <c r="D4">
+        <v>17.4</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -455,8 +455,8 @@
       <c r="C5">
         <v>4</v>
       </c>
-      <c r="D5" t="s">
-        <v>4</v>
+      <c r="D5">
+        <v>20.3</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -469,8 +469,8 @@
       <c r="C6">
         <v>5</v>
       </c>
-      <c r="D6" t="s">
-        <v>4</v>
+      <c r="D6">
+        <v>18.9</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -553,8 +553,8 @@
       <c r="C12">
         <v>11</v>
       </c>
-      <c r="D12" t="s">
-        <v>4</v>
+      <c r="D12">
+        <v>19.2</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -567,8 +567,8 @@
       <c r="C13">
         <v>12</v>
       </c>
-      <c r="D13" t="s">
-        <v>4</v>
+      <c r="D13">
+        <v>18.3</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -581,8 +581,8 @@
       <c r="C14">
         <v>13</v>
       </c>
-      <c r="D14" t="s">
-        <v>4</v>
+      <c r="D14">
+        <v>19.2</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -595,8 +595,8 @@
       <c r="C15">
         <v>14</v>
       </c>
-      <c r="D15" t="s">
-        <v>4</v>
+      <c r="D15">
+        <v>19.4</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -609,8 +609,8 @@
       <c r="C16">
         <v>15</v>
       </c>
-      <c r="D16" t="s">
-        <v>4</v>
+      <c r="D16">
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -623,8 +623,8 @@
       <c r="C17">
         <v>16</v>
       </c>
-      <c r="D17" t="s">
-        <v>4</v>
+      <c r="D17">
+        <v>19.1</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -637,8 +637,8 @@
       <c r="C18">
         <v>17</v>
       </c>
-      <c r="D18" t="s">
-        <v>4</v>
+      <c r="D18">
+        <v>19.6</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -651,8 +651,8 @@
       <c r="C19">
         <v>18</v>
       </c>
-      <c r="D19" t="s">
-        <v>4</v>
+      <c r="D19">
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -665,8 +665,8 @@
       <c r="C20">
         <v>19</v>
       </c>
-      <c r="D20" t="s">
-        <v>4</v>
+      <c r="D20">
+        <v>16.8</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -679,8 +679,8 @@
       <c r="C21">
         <v>20</v>
       </c>
-      <c r="D21" t="s">
-        <v>4</v>
+      <c r="D21">
+        <v>18.2</v>
       </c>
     </row>
     <row r="22" spans="1:4">

--- a/results/04_final_refined_daily_hydroclimate_data/508/Dry_bulb_temp_06h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/508/Dry_bulb_temp_06h00_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="5">
   <si>
     <t>Year</t>
   </si>
@@ -623,8 +623,8 @@
       <c r="C17">
         <v>16</v>
       </c>
-      <c r="D17">
-        <v>19.1</v>
+      <c r="D17" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -637,8 +637,8 @@
       <c r="C18">
         <v>17</v>
       </c>
-      <c r="D18">
-        <v>19.6</v>
+      <c r="D18" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -651,8 +651,8 @@
       <c r="C19">
         <v>18</v>
       </c>
-      <c r="D19">
-        <v>18</v>
+      <c r="D19" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -665,8 +665,8 @@
       <c r="C20">
         <v>19</v>
       </c>
-      <c r="D20">
-        <v>16.8</v>
+      <c r="D20" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -679,8 +679,8 @@
       <c r="C21">
         <v>20</v>
       </c>
-      <c r="D21">
-        <v>18.2</v>
+      <c r="D21" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:4">

--- a/results/04_final_refined_daily_hydroclimate_data/508/Dry_bulb_temp_06h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/508/Dry_bulb_temp_06h00_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="5">
   <si>
     <t>Year</t>
   </si>
@@ -553,8 +553,8 @@
       <c r="C12">
         <v>11</v>
       </c>
-      <c r="D12">
-        <v>19.2</v>
+      <c r="D12" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -567,8 +567,8 @@
       <c r="C13">
         <v>12</v>
       </c>
-      <c r="D13">
-        <v>18.3</v>
+      <c r="D13" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -581,8 +581,8 @@
       <c r="C14">
         <v>13</v>
       </c>
-      <c r="D14">
-        <v>19.2</v>
+      <c r="D14" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -595,8 +595,8 @@
       <c r="C15">
         <v>14</v>
       </c>
-      <c r="D15">
-        <v>19.4</v>
+      <c r="D15" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -609,8 +609,8 @@
       <c r="C16">
         <v>15</v>
       </c>
-      <c r="D16">
-        <v>18</v>
+      <c r="D16" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -623,8 +623,8 @@
       <c r="C17">
         <v>16</v>
       </c>
-      <c r="D17" t="s">
-        <v>4</v>
+      <c r="D17">
+        <v>19.1</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -637,8 +637,8 @@
       <c r="C18">
         <v>17</v>
       </c>
-      <c r="D18" t="s">
-        <v>4</v>
+      <c r="D18">
+        <v>19.6</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -651,8 +651,8 @@
       <c r="C19">
         <v>18</v>
       </c>
-      <c r="D19" t="s">
-        <v>4</v>
+      <c r="D19">
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -665,8 +665,8 @@
       <c r="C20">
         <v>19</v>
       </c>
-      <c r="D20" t="s">
-        <v>4</v>
+      <c r="D20">
+        <v>16.8</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -679,8 +679,8 @@
       <c r="C21">
         <v>20</v>
       </c>
-      <c r="D21" t="s">
-        <v>4</v>
+      <c r="D21">
+        <v>18.2</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -707,8 +707,8 @@
       <c r="C23">
         <v>22</v>
       </c>
-      <c r="D23" t="s">
-        <v>4</v>
+      <c r="D23">
+        <v>18.8</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -721,8 +721,8 @@
       <c r="C24">
         <v>23</v>
       </c>
-      <c r="D24" t="s">
-        <v>4</v>
+      <c r="D24">
+        <v>19.7</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -735,8 +735,8 @@
       <c r="C25">
         <v>24</v>
       </c>
-      <c r="D25" t="s">
-        <v>4</v>
+      <c r="D25">
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -749,8 +749,8 @@
       <c r="C26">
         <v>25</v>
       </c>
-      <c r="D26" t="s">
-        <v>4</v>
+      <c r="D26">
+        <v>18.7</v>
       </c>
     </row>
     <row r="27" spans="1:4">
